--- a/dcf/COHR.xlsx
+++ b/dcf/COHR.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1105,25 +1105,25 @@
         </is>
       </c>
       <c r="B4" s="52" t="n">
-        <v>0.1208574808941716</v>
+        <v>0.1205198249193393</v>
       </c>
       <c r="C4" s="52" t="n">
-        <v>0.1258574808941716</v>
+        <v>0.1255198249193393</v>
       </c>
       <c r="D4" s="52" t="n">
-        <v>0.1308574808941716</v>
+        <v>0.1305198249193393</v>
       </c>
       <c r="E4" s="52" t="n">
-        <v>0.1358574808941716</v>
+        <v>0.1355198249193393</v>
       </c>
       <c r="F4" s="52" t="n">
-        <v>0.1408574808941716</v>
+        <v>0.1405198249193393</v>
       </c>
       <c r="G4" s="52" t="n">
-        <v>0.1458574808941716</v>
+        <v>0.1455198249193393</v>
       </c>
       <c r="H4" s="52" t="n">
-        <v>0.1508574808941716</v>
+        <v>0.1505198249193394</v>
       </c>
     </row>
     <row r="5">
@@ -1131,25 +1131,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="54" t="n">
-        <v>254.5063395369442</v>
+        <v>192.9424763960803</v>
       </c>
       <c r="C5" s="54" t="n">
-        <v>244.7905821586782</v>
+        <v>185.7350460100083</v>
       </c>
       <c r="D5" s="54" t="n">
-        <v>235.5096340892605</v>
+        <v>178.8472139156561</v>
       </c>
       <c r="E5" s="54" t="n">
-        <v>226.6417484658326</v>
+        <v>172.2630589155663</v>
       </c>
       <c r="F5" s="54" t="n">
-        <v>218.1663669035222</v>
+        <v>165.9675282197744</v>
       </c>
       <c r="G5" s="54" t="n">
-        <v>210.0640493648717</v>
+        <v>159.9463862541814</v>
       </c>
       <c r="H5" s="54" t="n">
-        <v>202.3164084624591</v>
+        <v>154.1861667032008</v>
       </c>
     </row>
     <row r="6">
@@ -1157,25 +1157,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="54" t="n">
-        <v>273.6322553394109</v>
+        <v>206.8389000517149</v>
       </c>
       <c r="C6" s="54" t="n">
-        <v>263.0838801212474</v>
+        <v>199.0263319897073</v>
       </c>
       <c r="D6" s="54" t="n">
-        <v>253.0100122661128</v>
+        <v>191.5622227837469</v>
       </c>
       <c r="E6" s="54" t="n">
-        <v>243.3868490353282</v>
+        <v>184.4291561749281</v>
       </c>
       <c r="F6" s="54" t="n">
-        <v>234.1918910127532</v>
+        <v>177.6106678526288</v>
       </c>
       <c r="G6" s="54" t="n">
-        <v>225.4038650949753</v>
+        <v>171.0911892573067</v>
       </c>
       <c r="H6" s="54" t="n">
-        <v>217.0026523543065</v>
+        <v>164.855994937542</v>
       </c>
     </row>
     <row r="7">
@@ -1183,25 +1183,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="54" t="n">
-        <v>292.7581711418777</v>
+        <v>220.7353237073496</v>
       </c>
       <c r="C7" s="54" t="n">
-        <v>281.3771780838167</v>
+        <v>212.3176179694061</v>
       </c>
       <c r="D7" s="54" t="n">
-        <v>270.5103904429652</v>
+        <v>204.2772316518377</v>
       </c>
       <c r="E7" s="54" t="n">
-        <v>260.1319496048237</v>
+        <v>196.5952534342898</v>
       </c>
       <c r="F7" s="54" t="n">
-        <v>250.2174151219842</v>
+        <v>189.2538074854833</v>
       </c>
       <c r="G7" s="54" t="n">
-        <v>240.743680825079</v>
+        <v>182.2359922604321</v>
       </c>
       <c r="H7" s="54" t="n">
-        <v>231.6888962461539</v>
+        <v>175.5258231718832</v>
       </c>
     </row>
     <row r="8">
@@ -1209,25 +1209,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="54" t="n">
-        <v>311.8840869443444</v>
+        <v>234.6317473629842</v>
       </c>
       <c r="C8" s="54" t="n">
-        <v>299.6704760463859</v>
+        <v>225.608903949105</v>
       </c>
       <c r="D8" s="54" t="n">
-        <v>288.0107686198176</v>
+        <v>216.9922405199285</v>
       </c>
       <c r="E8" s="55" t="n">
-        <v>276.8770501743193</v>
+        <v>208.7613506936516</v>
       </c>
       <c r="F8" s="54" t="n">
-        <v>266.2429392312152</v>
+        <v>200.8969471183376</v>
       </c>
       <c r="G8" s="54" t="n">
-        <v>256.0834965551827</v>
+        <v>193.3807952635574</v>
       </c>
       <c r="H8" s="54" t="n">
-        <v>246.3751401380013</v>
+        <v>186.1956514062243</v>
       </c>
     </row>
     <row r="9">
@@ -1235,77 +1235,77 @@
         <v>13</v>
       </c>
       <c r="B9" s="54" t="n">
-        <v>331.010002746811</v>
+        <v>248.5281710186188</v>
       </c>
       <c r="C9" s="54" t="n">
-        <v>317.9637740089551</v>
+        <v>238.9001899288039</v>
       </c>
       <c r="D9" s="54" t="n">
-        <v>305.5111467966699</v>
+        <v>229.7072493880192</v>
       </c>
       <c r="E9" s="54" t="n">
-        <v>293.6221507438148</v>
+        <v>220.9274479530134</v>
       </c>
       <c r="F9" s="54" t="n">
-        <v>282.2684633404462</v>
+        <v>212.540086751192</v>
       </c>
       <c r="G9" s="54" t="n">
-        <v>271.4233122852863</v>
+        <v>204.5255982666827</v>
       </c>
       <c r="H9" s="54" t="n">
-        <v>261.0613840298487</v>
+        <v>196.8654796405655</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="53" t="n">
         <v>14</v>
       </c>
-      <c r="B10" s="8" t="n">
-        <v>350.1359185492778</v>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>336.2570719715243</v>
+      <c r="B10" s="54" t="n">
+        <v>262.4245946742535</v>
+      </c>
+      <c r="C10" s="54" t="n">
+        <v>252.1914759085028</v>
       </c>
       <c r="D10" s="54" t="n">
-        <v>323.0115249735222</v>
+        <v>242.42225825611</v>
       </c>
       <c r="E10" s="54" t="n">
-        <v>310.3672513133104</v>
+        <v>233.0935452123752</v>
       </c>
       <c r="F10" s="54" t="n">
-        <v>298.2939874496773</v>
+        <v>224.1832263840464</v>
       </c>
       <c r="G10" s="54" t="n">
-        <v>286.7631280153901</v>
+        <v>215.6704012698081</v>
       </c>
       <c r="H10" s="54" t="n">
-        <v>275.7476279216961</v>
+        <v>207.5353078749067</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="53" t="n">
         <v>15</v>
       </c>
-      <c r="B11" s="8" t="n">
-        <v>369.2618343517445</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>354.5503699340935</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>340.5119031503746</v>
+      <c r="B11" s="54" t="n">
+        <v>276.3210183298881</v>
+      </c>
+      <c r="C11" s="54" t="n">
+        <v>265.4827618882017</v>
+      </c>
+      <c r="D11" s="54" t="n">
+        <v>255.1372671242008</v>
       </c>
       <c r="E11" s="54" t="n">
-        <v>327.1123518828059</v>
+        <v>245.259642471737</v>
       </c>
       <c r="F11" s="54" t="n">
-        <v>314.3195115589083</v>
+        <v>235.8263660169008</v>
       </c>
       <c r="G11" s="54" t="n">
-        <v>302.1029437454937</v>
+        <v>226.8152042729334</v>
       </c>
       <c r="H11" s="54" t="n">
-        <v>290.4338718135435</v>
+        <v>218.2051361092479</v>
       </c>
     </row>
     <row r="13">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="B13" s="54" t="n">
-        <v>333.3599853515625</v>
+        <v>314.9800109863281</v>
       </c>
     </row>
     <row r="14">
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="B14" s="56" t="n">
-        <v>0.1358574808941716</v>
+        <v>0.1355198249193393</v>
       </c>
       <c r="C14" s="57" t="n">
         <v>12</v>
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="I8" s="49" t="n">
-        <v>0.9749960948047653</v>
+        <v>0.9852834735875662</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24410,7 +24410,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>333.3599853515625</v>
+        <v>314.9800109863281</v>
       </c>
     </row>
     <row r="49">
@@ -24420,7 +24420,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1.15</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24572,13 +24572,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>276.8770501743193</v>
+        <v>208.7613506936516</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>390.2804655194591</v>
+        <v>288.9447273975278</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>191.3334811891783</v>
+        <v>147.0399572494612</v>
       </c>
     </row>
     <row r="59">
